--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582074</v>
+        <v>121582094</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568233</v>
+        <v>568276</v>
       </c>
       <c r="R2" t="n">
-        <v>6993506</v>
+        <v>6993470</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582025</v>
+        <v>121582072</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568332</v>
+        <v>568211</v>
       </c>
       <c r="R3" t="n">
-        <v>6993474</v>
+        <v>6993534</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582065</v>
+        <v>121582050</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568190</v>
+        <v>568340</v>
       </c>
       <c r="R4" t="n">
-        <v>6993524</v>
+        <v>6993508</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582050</v>
+        <v>121582024</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568340</v>
+        <v>568334</v>
       </c>
       <c r="R5" t="n">
-        <v>6993508</v>
+        <v>6993514</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582072</v>
+        <v>121582074</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568211</v>
+        <v>568233</v>
       </c>
       <c r="R6" t="n">
-        <v>6993534</v>
+        <v>6993506</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582094</v>
+        <v>121582029</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568276</v>
+        <v>568332</v>
       </c>
       <c r="R7" t="n">
-        <v>6993470</v>
+        <v>6993474</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582067</v>
+        <v>121582065</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568216</v>
+        <v>568190</v>
       </c>
       <c r="R8" t="n">
-        <v>6993473</v>
+        <v>6993524</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582024</v>
+        <v>121582067</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568334</v>
+        <v>568216</v>
       </c>
       <c r="R9" t="n">
-        <v>6993514</v>
+        <v>6993473</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582050</v>
+        <v>121582029</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568340</v>
+        <v>568332</v>
       </c>
       <c r="R4" t="n">
-        <v>6993508</v>
+        <v>6993474</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582074</v>
+        <v>121582065</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568233</v>
+        <v>568190</v>
       </c>
       <c r="R6" t="n">
-        <v>6993506</v>
+        <v>6993524</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582029</v>
+        <v>121582074</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568332</v>
+        <v>568233</v>
       </c>
       <c r="R7" t="n">
-        <v>6993474</v>
+        <v>6993506</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582065</v>
+        <v>121582050</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568190</v>
+        <v>568340</v>
       </c>
       <c r="R8" t="n">
-        <v>6993524</v>
+        <v>6993508</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582094</v>
+        <v>121582067</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568276</v>
+        <v>568216</v>
       </c>
       <c r="R2" t="n">
-        <v>6993470</v>
+        <v>6993473</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582072</v>
+        <v>121582029</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568211</v>
+        <v>568332</v>
       </c>
       <c r="R3" t="n">
-        <v>6993534</v>
+        <v>6993474</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582029</v>
+        <v>121582024</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568332</v>
+        <v>568334</v>
       </c>
       <c r="R4" t="n">
-        <v>6993474</v>
+        <v>6993514</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582024</v>
+        <v>121582065</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568334</v>
+        <v>568190</v>
       </c>
       <c r="R5" t="n">
-        <v>6993514</v>
+        <v>6993524</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582065</v>
+        <v>121582050</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568190</v>
+        <v>568340</v>
       </c>
       <c r="R6" t="n">
-        <v>6993524</v>
+        <v>6993508</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582050</v>
+        <v>121582094</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568340</v>
+        <v>568276</v>
       </c>
       <c r="R8" t="n">
-        <v>6993508</v>
+        <v>6993470</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582067</v>
+        <v>121582072</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568216</v>
+        <v>568211</v>
       </c>
       <c r="R9" t="n">
-        <v>6993473</v>
+        <v>6993534</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582067</v>
+        <v>121582094</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568216</v>
+        <v>568276</v>
       </c>
       <c r="R2" t="n">
-        <v>6993473</v>
+        <v>6993470</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582029</v>
+        <v>121582072</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568332</v>
+        <v>568211</v>
       </c>
       <c r="R3" t="n">
-        <v>6993474</v>
+        <v>6993534</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582065</v>
+        <v>121582074</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568190</v>
+        <v>568233</v>
       </c>
       <c r="R5" t="n">
-        <v>6993524</v>
+        <v>6993506</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582050</v>
+        <v>121582029</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568340</v>
+        <v>568332</v>
       </c>
       <c r="R6" t="n">
-        <v>6993508</v>
+        <v>6993474</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582074</v>
+        <v>121582067</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568233</v>
+        <v>568216</v>
       </c>
       <c r="R7" t="n">
-        <v>6993506</v>
+        <v>6993473</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582094</v>
+        <v>121582050</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568276</v>
+        <v>568340</v>
       </c>
       <c r="R8" t="n">
-        <v>6993470</v>
+        <v>6993508</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582072</v>
+        <v>121582065</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568211</v>
+        <v>568190</v>
       </c>
       <c r="R9" t="n">
-        <v>6993534</v>
+        <v>6993524</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>121582094</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121582072</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>121582024</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582074</v>
+        <v>121582050</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568233</v>
+        <v>568340</v>
       </c>
       <c r="R5" t="n">
-        <v>6993506</v>
+        <v>6993508</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>121582029</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582067</v>
+        <v>121582065</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568216</v>
+        <v>568190</v>
       </c>
       <c r="R7" t="n">
-        <v>6993473</v>
+        <v>6993524</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582050</v>
+        <v>121582074</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568340</v>
+        <v>568233</v>
       </c>
       <c r="R8" t="n">
-        <v>6993508</v>
+        <v>6993506</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582065</v>
+        <v>121582067</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568190</v>
+        <v>568216</v>
       </c>
       <c r="R9" t="n">
-        <v>6993524</v>
+        <v>6993473</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1528,6 +1528,108 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121696881</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79697</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Måckelmyrberget, Råssåkerberget, Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>568233</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6993506</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582025</v>
+        <v>121582072</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568332</v>
+        <v>568211</v>
       </c>
       <c r="R2" t="n">
-        <v>6993474</v>
+        <v>6993534</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582065</v>
+        <v>121582024</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568190</v>
+        <v>568334</v>
       </c>
       <c r="R3" t="n">
-        <v>6993524</v>
+        <v>6993514</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582050</v>
+        <v>121582067</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568340</v>
+        <v>568216</v>
       </c>
       <c r="R4" t="n">
-        <v>6993508</v>
+        <v>6993473</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582094</v>
+        <v>121582050</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568276</v>
+        <v>568340</v>
       </c>
       <c r="R5" t="n">
-        <v>6993470</v>
+        <v>6993508</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582072</v>
+        <v>121582065</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568211</v>
+        <v>568190</v>
       </c>
       <c r="R6" t="n">
-        <v>6993534</v>
+        <v>6993524</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582067</v>
+        <v>121582029</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568216</v>
+        <v>568332</v>
       </c>
       <c r="R7" t="n">
-        <v>6993473</v>
+        <v>6993474</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582074</v>
+        <v>121582094</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568233</v>
+        <v>568276</v>
       </c>
       <c r="R8" t="n">
-        <v>6993506</v>
+        <v>6993470</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582024</v>
+        <v>121582074</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568334</v>
+        <v>568233</v>
       </c>
       <c r="R9" t="n">
-        <v>6993514</v>
+        <v>6993506</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582072</v>
+        <v>121582094</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568211</v>
+        <v>568276</v>
       </c>
       <c r="R2" t="n">
-        <v>6993534</v>
+        <v>6993470</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582024</v>
+        <v>121582029</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568334</v>
+        <v>568332</v>
       </c>
       <c r="R3" t="n">
-        <v>6993514</v>
+        <v>6993474</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582067</v>
+        <v>121582074</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568216</v>
+        <v>568233</v>
       </c>
       <c r="R4" t="n">
-        <v>6993473</v>
+        <v>6993506</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582029</v>
+        <v>121582072</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568332</v>
+        <v>568211</v>
       </c>
       <c r="R7" t="n">
-        <v>6993474</v>
+        <v>6993534</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582094</v>
+        <v>121582024</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568276</v>
+        <v>568334</v>
       </c>
       <c r="R8" t="n">
-        <v>6993470</v>
+        <v>6993514</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582074</v>
+        <v>121582067</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568233</v>
+        <v>568216</v>
       </c>
       <c r="R9" t="n">
-        <v>6993506</v>
+        <v>6993473</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582094</v>
+        <v>121582067</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568276</v>
+        <v>568216</v>
       </c>
       <c r="R2" t="n">
-        <v>6993470</v>
+        <v>6993473</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582029</v>
+        <v>121582065</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568332</v>
+        <v>568190</v>
       </c>
       <c r="R3" t="n">
-        <v>6993474</v>
+        <v>6993524</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582074</v>
+        <v>121582025</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568233</v>
+        <v>568332</v>
       </c>
       <c r="R4" t="n">
-        <v>6993506</v>
+        <v>6993474</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582065</v>
+        <v>121582072</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568190</v>
+        <v>568211</v>
       </c>
       <c r="R6" t="n">
-        <v>6993524</v>
+        <v>6993534</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582072</v>
+        <v>121582024</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568211</v>
+        <v>568334</v>
       </c>
       <c r="R7" t="n">
-        <v>6993534</v>
+        <v>6993514</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582024</v>
+        <v>121582074</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568334</v>
+        <v>568233</v>
       </c>
       <c r="R8" t="n">
-        <v>6993514</v>
+        <v>6993506</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582067</v>
+        <v>121582094</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568216</v>
+        <v>568276</v>
       </c>
       <c r="R9" t="n">
-        <v>6993473</v>
+        <v>6993470</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582067</v>
+        <v>121582050</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568216</v>
+        <v>568340</v>
       </c>
       <c r="R2" t="n">
-        <v>6993473</v>
+        <v>6993508</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582065</v>
+        <v>121582025</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568190</v>
+        <v>568332</v>
       </c>
       <c r="R3" t="n">
-        <v>6993524</v>
+        <v>6993474</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582025</v>
+        <v>121582065</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568332</v>
+        <v>568190</v>
       </c>
       <c r="R4" t="n">
-        <v>6993474</v>
+        <v>6993524</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582050</v>
+        <v>121582094</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568340</v>
+        <v>568276</v>
       </c>
       <c r="R5" t="n">
-        <v>6993508</v>
+        <v>6993470</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582072</v>
+        <v>121582067</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568211</v>
+        <v>568216</v>
       </c>
       <c r="R6" t="n">
-        <v>6993534</v>
+        <v>6993473</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582024</v>
+        <v>121582074</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568334</v>
+        <v>568233</v>
       </c>
       <c r="R7" t="n">
-        <v>6993514</v>
+        <v>6993506</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582074</v>
+        <v>121582024</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568233</v>
+        <v>568334</v>
       </c>
       <c r="R8" t="n">
-        <v>6993506</v>
+        <v>6993514</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582094</v>
+        <v>121582072</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568276</v>
+        <v>568211</v>
       </c>
       <c r="R9" t="n">
-        <v>6993470</v>
+        <v>6993534</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582050</v>
+        <v>121582072</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568340</v>
+        <v>568211</v>
       </c>
       <c r="R2" t="n">
-        <v>6993508</v>
+        <v>6993534</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582067</v>
+        <v>121582074</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568216</v>
+        <v>568233</v>
       </c>
       <c r="R6" t="n">
-        <v>6993473</v>
+        <v>6993506</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582074</v>
+        <v>121582067</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568233</v>
+        <v>568216</v>
       </c>
       <c r="R7" t="n">
-        <v>6993506</v>
+        <v>6993473</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582024</v>
+        <v>121582050</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568334</v>
+        <v>568340</v>
       </c>
       <c r="R8" t="n">
-        <v>6993514</v>
+        <v>6993508</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582072</v>
+        <v>121582024</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568211</v>
+        <v>568334</v>
       </c>
       <c r="R9" t="n">
-        <v>6993534</v>
+        <v>6993514</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582072</v>
+        <v>121582074</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568211</v>
+        <v>568233</v>
       </c>
       <c r="R2" t="n">
-        <v>6993534</v>
+        <v>6993506</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582025</v>
+        <v>121582065</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568332</v>
+        <v>568190</v>
       </c>
       <c r="R3" t="n">
-        <v>6993474</v>
+        <v>6993524</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582065</v>
+        <v>121582024</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568190</v>
+        <v>568334</v>
       </c>
       <c r="R4" t="n">
-        <v>6993524</v>
+        <v>6993514</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582094</v>
+        <v>121582029</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568276</v>
+        <v>568332</v>
       </c>
       <c r="R5" t="n">
-        <v>6993470</v>
+        <v>6993474</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582074</v>
+        <v>121582072</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568233</v>
+        <v>568211</v>
       </c>
       <c r="R6" t="n">
-        <v>6993506</v>
+        <v>6993534</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582067</v>
+        <v>121582050</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568216</v>
+        <v>568340</v>
       </c>
       <c r="R7" t="n">
-        <v>6993473</v>
+        <v>6993508</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582050</v>
+        <v>121582094</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568340</v>
+        <v>568276</v>
       </c>
       <c r="R8" t="n">
-        <v>6993508</v>
+        <v>6993470</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582024</v>
+        <v>121582067</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568334</v>
+        <v>568216</v>
       </c>
       <c r="R9" t="n">
-        <v>6993514</v>
+        <v>6993473</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582072</v>
+        <v>121582050</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1147,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568211</v>
+        <v>568340</v>
       </c>
       <c r="R6" t="n">
-        <v>6993534</v>
+        <v>6993508</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582050</v>
+        <v>121582094</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568340</v>
+        <v>568276</v>
       </c>
       <c r="R7" t="n">
-        <v>6993508</v>
+        <v>6993470</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582094</v>
+        <v>121582072</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568276</v>
+        <v>568211</v>
       </c>
       <c r="R8" t="n">
-        <v>6993470</v>
+        <v>6993534</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121582074</v>
+        <v>121582067</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568233</v>
+        <v>568216</v>
       </c>
       <c r="R2" t="n">
-        <v>6993506</v>
+        <v>6993473</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121582065</v>
+        <v>121582029</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568190</v>
+        <v>568332</v>
       </c>
       <c r="R3" t="n">
-        <v>6993524</v>
+        <v>6993474</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121582024</v>
+        <v>121582050</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568334</v>
+        <v>568340</v>
       </c>
       <c r="R4" t="n">
-        <v>6993514</v>
+        <v>6993508</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121582029</v>
+        <v>121582024</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568332</v>
+        <v>568334</v>
       </c>
       <c r="R5" t="n">
-        <v>6993474</v>
+        <v>6993514</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121582050</v>
+        <v>121582065</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568340</v>
+        <v>568190</v>
       </c>
       <c r="R6" t="n">
-        <v>6993508</v>
+        <v>6993524</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121582094</v>
+        <v>121582074</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568276</v>
+        <v>568233</v>
       </c>
       <c r="R7" t="n">
-        <v>6993470</v>
+        <v>6993506</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121582072</v>
+        <v>121582094</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568211</v>
+        <v>568276</v>
       </c>
       <c r="R8" t="n">
-        <v>6993534</v>
+        <v>6993470</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121582067</v>
+        <v>121582072</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568216</v>
+        <v>568211</v>
       </c>
       <c r="R9" t="n">
-        <v>6993473</v>
+        <v>6993534</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>121696881</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>79710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,117 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124875080</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Måckelmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568398</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6993588</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -1636,7 +1636,7 @@
         <v>124875080</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 16044-2020 artfynd.xlsx
+++ b/artfynd/A 16044-2020 artfynd.xlsx
@@ -1638,11 +1638,6 @@
       <c r="B11" t="n">
         <v>57632</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>
